--- a/Result/profitability/6128.xlsx
+++ b/Result/profitability/6128.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.29</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.9674999999999999</v>
+        <v>-0.9925</v>
       </c>
       <c r="N2" t="n">
-        <v>38.73625</v>
+        <v>38.8725</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.53</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.97375</v>
+        <v>-1.01125</v>
       </c>
       <c r="N3" t="n">
-        <v>37.62</v>
+        <v>37.86</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -792,7 +792,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.54</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9912499999999999</v>
+        <v>-1.00375</v>
       </c>
       <c r="N4" t="n">
-        <v>36.9075</v>
+        <v>37.21250000000001</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.72</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9612499999999998</v>
+        <v>-0.9599999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>36.71250000000001</v>
+        <v>36.8625</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.72</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9174999999999998</v>
+        <v>0.4250000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>36.82125</v>
+        <v>37.6275</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1152,13 +1152,13 @@
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.99</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5012500000000001</v>
+        <v>0.5562500000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>37.8825</v>
+        <v>38.52875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1288,7 +1288,7 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
         <v>98.2</v>
@@ -1391,10 +1391,10 @@
         <v>1.61</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7100000000000001</v>
+        <v>0.7225000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>38.87875</v>
+        <v>39.19500000000001</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1645,10 +1645,10 @@
         <v>0.93</v>
       </c>
       <c r="M10" t="n">
-        <v>0.8662500000000002</v>
+        <v>0.8662500000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>40.025</v>
+        <v>40.02500000000001</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1772,7 +1772,7 @@
         <v>1.21</v>
       </c>
       <c r="M11" t="n">
-        <v>0.9512500000000002</v>
+        <v>0.95125</v>
       </c>
       <c r="N11" t="n">
         <v>40.98625</v>
@@ -1902,7 +1902,7 @@
         <v>1.0025</v>
       </c>
       <c r="N12" t="n">
-        <v>41.78875</v>
+        <v>41.78874999999999</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -2026,10 +2026,10 @@
         <v>0.6</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9875000000000002</v>
+        <v>0.9875</v>
       </c>
       <c r="N13" t="n">
-        <v>41.9275</v>
+        <v>41.92749999999999</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6128</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1278</v>
+      </c>
+      <c r="D75" t="n">
+        <v>736</v>
+      </c>
+      <c r="E75" t="n">
+        <v>543</v>
+      </c>
+      <c r="F75" t="n">
+        <v>42.45</v>
+      </c>
+      <c r="G75" t="n">
+        <v>76</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>5.97%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J75" t="n">
+        <v>60</v>
+      </c>
+      <c r="K75" t="n">
+        <v>48</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.9562499999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>39.85</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.357142857142857</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.530000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.06337675350701399</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.01000000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.02702702702702697</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.200000000000003</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.02909090909090906</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
